--- a/analise_formatada.xlsx
+++ b/analise_formatada.xlsx
@@ -460,12 +460,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Afirmação</t>
+          <t>Prática</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Atributo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -504,12 +504,12 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Direta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Indireta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>Direta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Indireta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Direta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Indireta Média</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>(0.5668202764976958, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>(0.046153846153846156, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>(-0.021592442645074223, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>(0.511520737327189, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>(-0.028846153846153848, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>(0.07422402159244265, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>(0.6589861751152074, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>(0.0125, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>(0.0951417004048583, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>(0.4093701996927803, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>(0.04326923076923077, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>(0.0931174089068826, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>(0.49615975422427033, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>(-0.0057692307692307696, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>(0.058029689608636977, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>(0.5092165898617511, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>(-0.09615384615384616, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>(-0.0708502024291498, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>(0.5837173579109063, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>(-0.1778846153846154, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>(0.004723346828609987, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>(0.49539170506912444, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>(-0.04038461538461539, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>(0.11336032388663968, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>(0.46927803379416283, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>(-0.025961538461538463, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>(-0.012145748987854251, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>(0.46006144393241166, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>(-0.009615384615384616, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>(-0.150472334682861, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>(0.4539170506912442, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>(-0.13942307692307693, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>(-0.001349527665317139, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>(0.5353302611367128, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>(-0.025, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>(0.07354925775978408, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>(0.4646697388632873, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>(0.05480769230769231, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>(0.1329284750337382, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>(0.423963133640553, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>(-0.041346153846153845, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>(-0.19973009446693657, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>(0.48540706605222733, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>(-0.13365384615384615, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>(0.010121457489878543, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>(0.4554531490015361, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>(0.03365384615384615, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>(0.09244264507422402, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>(0.5384024577572964, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>(-0.058653846153846154, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>(0.07489878542510121, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>(0.5046082949308756, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>(0.0009615384615384616, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>(-0.07017543859649122, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>(0.6290322580645161, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>(-0.07403846153846154, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>(0.02631578947368421, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>(0.4485407066052227, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>(0.014423076923076924, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>(0.09851551956815115, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>(0.6290322580645161, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>(-0.18557692307692308, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>(0.016869095816464237, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>(0.5522273425499232, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>(-0.23365384615384616, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>(-0.04116059379217274, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>(0.5468509984639017, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>(-0.06923076923076923, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>(0.11740890688259109, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>(0.4324116743471582, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>(0.08846153846153847, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>(0.26653171390013497, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>(0.49923195084485406, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>(-0.12980769230769232, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>(0.09109311740890688, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>(0.5691244239631337, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>(-0.0028846153846153848, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>(-0.04723346828609987, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>(0.5606758832565284, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>(-0.2644230769230769, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>(-0.0310391363022942, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>(0.41397849462365593, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>(0.016346153846153847, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>(0.10323886639676114, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>(0.5345622119815668, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>(-0.07307692307692308, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>(0.05398110661268556, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>(0.5768049155145929, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>(-0.015384615384615385, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>(-0.0020242914979757085, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>(0.6190476190476191, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>(-0.15096153846153845, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>(0.020917678812415654, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>(0.500768049155146, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>(0.026923076923076925, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>(0.044534412955465584, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>(0.5714285714285714, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>(-0.07211538461538461, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>(-0.1592442645074224, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>(0.5445468509984639, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>(0.08942307692307692, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>(-0.08434547908232119, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>(0.5675883256528418, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>(-0.0057692307692307696, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>(-0.014844804318488529, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>(0.47081413210445466, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>(0.10192307692307692, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>(0.13022941970310392, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>(0.5460829493087558, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>(-0.0028846153846153848, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>(-0.12010796221322537, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>(0.5952380952380952, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>(0.04423076923076923, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>(-0.11740890688259109, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>(0.6996927803379416, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>(-0.17211538461538461, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>(0.0310391363022942, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>(0.5476190476190477, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>(-0.0673076923076923, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>(0.05263157894736842, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>(0.2887864823348694, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>(-0.08269230769230769, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>(0.10796221322537113, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>(0.47081413210445466, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>(0.0, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>(-0.0728744939271255, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>(0.4062980030721966, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>(-0.19903846153846153, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>(0.038461538461538464, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>(0.4508448540706605, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>(0.052884615384615384, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>(0.09919028340080972, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>(0.3778801843317972, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>(-0.10961538461538461, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>(-0.2483130904183536, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>(0.46390168970814133, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>(-0.046153846153846156, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>(-0.31309041835357626, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>(0.3717357910906298, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>(-0.28173076923076923, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>(-0.09446693657219973, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>(0.4500768049155146, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>(0.11923076923076924, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>(0.13765182186234817, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>(0.5821812596006144, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>(-0.03653846153846154, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>(-0.13225371120107962, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>(0.6566820276497696, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>(-0.08365384615384615, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>(-0.08502024291497975, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>(0.6451612903225806, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>(-0.14134615384615384, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>(0.1329284750337382, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>(0.6505376344086021, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>(-0.08173076923076923, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>(0.038461538461538464, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>(0.4162826420890937, 'medium')</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>(0.11634615384615385, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>(-0.018893387314439947, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>(0.49001536098310294, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>(0.0125, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>(-0.09851551956815115, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>(0.4915514592933948, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>(-0.11538461538461539, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>(-0.02631578947368421, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>(0.5906298003072197, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>(-0.025961538461538463, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>(0.17071524966261808, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>(0.5368663594470046, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>(-0.03173076923076923, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>(0.09716599190283401, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>(0.6397849462365591, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>(0.0057692307692307696, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>(0.011470985155195682, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>(0.619815668202765, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>(-0.1, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>(0.13832658569500675, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>(0.5422427035330261, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>(0.06538461538461539, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>(0.10526315789473684, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>(0.522273425499232, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>(0.07115384615384615, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>(0.20512820512820512, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>(0.6221198156682027, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>(-0.15096153846153845, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>(0.1417004048582996, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>(0.6758832565284179, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>(-0.19134615384615383, 'small')</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>(0.13900134952766532, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>(0.5138248847926268, 'large')</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>(-0.007692307692307693, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>(0.09244264507422402, 'negligible')</t>
+          <t>(-)*</t>
         </is>
       </c>
     </row>

--- a/analise_formatada.xlsx
+++ b/analise_formatada.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,8 +42,20 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9A9A9"/>
+        <bgColor rgb="00A9A9A9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -57,11 +69,60 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -70,6 +131,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -478,30 +549,30 @@
           <t>Direta vs. Indireta</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="5" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Grande vs. Pequena</t>
         </is>
       </c>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="5" t="n"/>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Especialista vs. Não especialista</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Média</t>
@@ -576,22 +647,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>11.252</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>5.591</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>13.170</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -601,17 +672,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11.498</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>10.829</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0.390</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -621,17 +692,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>11.049</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>11.345</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -641,6 +712,7 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -648,42 +720,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15.471</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9.293</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17.564</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>17.56</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15.326</t>
+          <t>15.33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16.329</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -693,17 +765,17 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16.253</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15.114</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -713,6 +785,7 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="7" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -720,42 +793,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8.787</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2.985</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10.752</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          <t>10.75</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8.819</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8.501</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -765,17 +838,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9.741</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8.351</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -785,6 +858,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" s="6" t="n"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -792,42 +866,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17.882</t>
+          <t>17.88</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13.710</t>
+          <t>13.71</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19.295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>19.30</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17.948</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17.655</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -837,17 +911,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18.925</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17.406</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -869,42 +943,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.814</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11.781</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          <t>11.78</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9.945</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.321</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -914,17 +988,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10.841</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9.644</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -934,6 +1008,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="7" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -941,42 +1016,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11.968</t>
+          <t>11.97</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5.719</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14.085</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          <t>14.09</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11.720</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13.223</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -986,17 +1061,17 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11.220</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12.310</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1006,6 +1081,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" s="7" t="n"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -1013,42 +1089,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5.543</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6.793</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+          <t>6.79</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5.039</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7.034</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1058,17 +1134,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5.403</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5.607</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1078,6 +1154,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="6" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -1085,42 +1162,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15.724</t>
+          <t>15.72</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11.022</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17.316</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15.658</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16.045</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1130,17 +1207,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16.538</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15.353</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1162,42 +1239,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11.089</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6.239</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12.732</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+          <t>12.73</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10.994</t>
+          <t>10.99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11.347</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1207,17 +1284,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10.869</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11.189</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1227,6 +1304,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="7" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -1234,42 +1312,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14.919</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16.812</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          <t>16.81</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14.932</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14.403</t>
+          <t>14.40</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1279,17 +1357,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13.625</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15.510</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1299,6 +1377,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="7" t="n"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -1306,42 +1385,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10.241</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5.484</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11.852</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+          <t>11.85</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9.752</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11.728</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1351,17 +1430,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10.362</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10.186</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1371,6 +1450,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="6" t="n"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -1378,42 +1458,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18.873</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.454</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20.709</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+          <t>20.71</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18.856</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18.975</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1423,17 +1503,17 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20.130</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18.300</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1455,42 +1535,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11.611</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6.532</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13.331</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11.758</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11.214</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1500,17 +1580,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12.745</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11.094</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1520,6 +1600,7 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="7" t="n"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -1527,42 +1608,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14.140</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9.077</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15.855</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+          <t>15.85</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14.133</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14.688</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1572,17 +1653,17 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12.313</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14.973</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1592,6 +1673,7 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="7" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -1599,42 +1681,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9.039</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4.203</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10.677</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+          <t>10.68</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8.677</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10.391</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1644,17 +1726,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9.268</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8.935</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1664,6 +1746,7 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" s="6" t="n"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -1671,42 +1754,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18.085</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13.542</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19.624</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+          <t>19.62</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18.115</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17.899</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0.420</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1716,17 +1799,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19.299</t>
+          <t>19.30</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17.532</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1748,42 +1831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10.915</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5.066</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12.897</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+          <t>12.90</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10.792</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11.815</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1793,17 +1876,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11.562</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10.620</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1813,6 +1896,7 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" s="7" t="n"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -1820,42 +1904,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15.063</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9.033</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17.105</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14.801</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16.094</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1865,17 +1949,17 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14.858</t>
+          <t>14.86</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15.156</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1885,6 +1969,7 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -1892,42 +1977,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7.935</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9.980</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+          <t>9.98</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7.626</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8.670</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1937,17 +2022,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8.280</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -1957,6 +2042,7 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" s="6" t="n"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -1964,42 +2050,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>17.411</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12.943</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18.924</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+          <t>18.92</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17.411</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17.259</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2009,17 +2095,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18.636</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16.853</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2041,42 +2127,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9.315</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2.663</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11.568</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+          <t>11.57</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8.759</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11.903</t>
+          <t>11.90</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0.880</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2086,17 +2172,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9.418</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9.268</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2106,6 +2192,7 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" s="7" t="n"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -2113,42 +2200,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10.583</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4.365</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12.690</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+          <t>12.69</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13.415</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2158,17 +2245,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10.051</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10.826</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2178,6 +2265,7 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" s="7" t="n"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -2185,42 +2273,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6.808</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8.717</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6.548</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7.464</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2230,17 +2318,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8.156</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6.193</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2250,6 +2338,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" s="6" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -2257,42 +2346,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14.122</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10.090</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15.488</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+          <t>15.49</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14.306</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13.362</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2302,20 +2391,20 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16.041</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13.247</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0.027</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+          <t>13.25</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
@@ -2334,42 +2423,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10.817</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5.590</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12.588</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+          <t>12.59</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10.448</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12.287</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2379,17 +2468,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11.810</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10.364</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2399,6 +2488,7 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" s="7" t="n"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -2406,42 +2496,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>15.554</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.099</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17.741</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+          <t>17.74</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15.355</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15.979</t>
+          <t>15.98</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2451,17 +2541,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15.021</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15.797</t>
+          <t>15.80</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2471,6 +2561,7 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" s="7" t="n"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -2478,42 +2569,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8.788</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3.532</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10.569</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+          <t>10.57</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8.094</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11.061</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2523,17 +2614,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8.567</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8.889</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2543,6 +2634,7 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" s="6" t="n"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -2550,42 +2642,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18.381</t>
+          <t>18.38</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14.328</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19.754</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18.274</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18.366</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2595,17 +2687,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19.413</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17.910</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2627,42 +2719,42 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12.975</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7.179</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14.938</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+          <t>14.94</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12.771</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13.775</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2672,17 +2764,17 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12.800</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2692,6 +2784,7 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" s="7" t="n"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -2699,42 +2792,42 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>16.68</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9.981</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18.945</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+          <t>18.94</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16.574</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16.433</t>
+          <t>16.43</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0.540</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2744,17 +2837,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16.589</t>
+          <t>16.59</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16.717</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2764,6 +2857,7 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" s="7" t="n"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -2771,42 +2865,42 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>11.668</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5.503</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13.756</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+          <t>13.76</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11.297</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12.984</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2816,17 +2910,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11.661</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11.671</t>
+          <t>11.67</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2836,6 +2930,7 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" s="6" t="n"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -2843,42 +2938,42 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>18.925</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>13.799</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20.661</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+          <t>20.66</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19.025</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18.555</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2888,17 +2983,17 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19.636</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18.600</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2920,42 +3015,42 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10.469</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4.567</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12.469</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10.173</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11.732</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2965,17 +3060,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9.130</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11.080</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -2985,6 +3080,7 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" s="7" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -2992,42 +3088,42 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>13.944</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7.672</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16.068</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14.141</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13.220</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3037,17 +3133,17 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13.243</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14.264</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3057,6 +3153,7 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" s="7" t="n"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -3064,42 +3161,42 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>8.552</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10.613</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+          <t>10.61</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8.523</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8.490</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3109,17 +3206,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8.710</t>
+          <t>8.71</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8.480</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3129,6 +3226,7 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" s="6" t="n"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -3136,42 +3234,42 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>16.982</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>12.723</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>18.425</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+          <t>18.42</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17.068</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16.009</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3181,17 +3279,17 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18.304</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16.379</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3213,42 +3311,42 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>11.067</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5.051</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13.105</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11.020</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11.393</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0.510</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3258,17 +3356,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9.721</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11.682</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3278,6 +3376,7 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" s="7" t="n"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -3285,42 +3384,42 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>14.556</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>6.689</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17.221</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14.694</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14.150</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3330,17 +3429,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12.872</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15.325</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3350,6 +3449,7 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" s="7" t="n"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -3357,42 +3457,42 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>8.534</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10.852</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+          <t>10.85</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8.039</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10.359</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3402,17 +3502,17 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9.097</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8.277</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -3422,6 +3522,7 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" s="6" t="n"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -3429,42 +3530,42 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>17.943</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>12.533</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19.776</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+          <t>19.78</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17.705</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18.408</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3474,17 +3575,17 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18.769</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17.567</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3506,42 +3607,42 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>10.626</t>
+          <t>10.63</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>7.516</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11.679</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>0.024</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+          <t>11.68</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10.351</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11.421</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3551,17 +3652,17 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11.657</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10.155</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3571,6 +3672,7 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" s="7" t="n"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -3578,42 +3680,42 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>15.229</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9.938</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>17.021</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+          <t>17.02</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15.074</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15.433</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3623,17 +3725,17 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14.625</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15.504</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3643,6 +3745,7 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" s="7" t="n"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -3650,42 +3753,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>9.702</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5.308</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11.190</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+          <t>11.19</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9.053</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>12.034</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3695,17 +3798,17 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>9.952</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9.587</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3715,6 +3818,7 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" s="6" t="n"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -3722,42 +3826,42 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>18.387</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>14.251</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19.788</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+          <t>19.79</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>18.516</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17.833</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3767,17 +3871,17 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19.450</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17.903</t>
+          <t>17.90</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3799,42 +3903,42 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>8.634</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>10.021</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+          <t>10.02</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8.621</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9.765</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3844,17 +3948,17 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>6.121</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9.780</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3864,6 +3968,7 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" s="7" t="n"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -3871,42 +3976,42 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>11.139</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5.512</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>13.045</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11.285</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>11.939</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3916,17 +4021,17 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7.619</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12.745</t>
+          <t>12.74</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0.990</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -3936,6 +4041,7 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" s="7" t="n"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -3943,42 +4049,42 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6.430</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2.832</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>7.648</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5.583</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9.424</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3988,17 +4094,17 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5.795</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6.719</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -4008,6 +4114,7 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" s="6" t="n"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -4015,42 +4122,42 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>16.040</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>11.474</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17.587</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+          <t>17.59</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16.296</t>
+          <t>16.30</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.094</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4060,17 +4167,17 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17.474</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15.386</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4092,42 +4199,42 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>12.964</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>6.847</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>15.035</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>12.992</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>13.371</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4137,17 +4244,17 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>11.505</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>13.629</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4157,6 +4264,7 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" s="7" t="n"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -4164,42 +4272,42 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>15.962</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>8.780</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>18.395</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+          <t>18.39</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15.731</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16.568</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4209,17 +4317,17 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>15.507</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16.170</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4229,6 +4337,7 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" s="7" t="n"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -4236,42 +4345,42 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>11.917</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>6.130</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>13.877</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+          <t>13.88</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11.582</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13.119</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>0.810</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4281,17 +4390,17 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13.063</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11.394</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -4301,6 +4410,7 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" s="6" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -4308,42 +4418,42 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>18.696</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>12.420</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>20.821</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+          <t>20.82</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18.508</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19.467</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4353,17 +4463,17 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19.375</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18.386</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4385,42 +4495,42 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>9.722</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5.382</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>11.192</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+          <t>11.19</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9.979</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8.646</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4430,17 +4540,17 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>9.398</t>
+          <t>9.40</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9.870</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -4450,6 +4560,7 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="7" t="n"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -4457,42 +4568,42 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>13.101</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>6.836</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>15.224</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+          <t>15.22</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>13.101</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>12.655</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4502,17 +4613,17 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12.166</t>
+          <t>12.17</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>13.528</t>
+          <t>13.53</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4522,6 +4633,7 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" s="7" t="n"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -4529,42 +4641,42 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7.575</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2.873</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>9.167</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
+          <t>9.17</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7.150</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>8.996</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4574,17 +4686,17 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>7.337</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>7.683</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4594,6 +4706,7 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" s="6" t="n"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -4601,42 +4714,42 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>17.558</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>11.710</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>19.539</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+          <t>19.54</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>17.400</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>17.647</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4646,17 +4759,17 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>19.518</t>
+          <t>19.52</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>16.664</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4678,42 +4791,42 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>11.866</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>5.881</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>13.894</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+          <t>13.89</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>11.677</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>12.470</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>0.580</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4723,17 +4836,17 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>12.768</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11.455</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4743,6 +4856,7 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" s="7" t="n"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -4750,42 +4864,42 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>16.467</t>
+          <t>16.47</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.870</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>19.379</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+          <t>19.38</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16.359</t>
+          <t>16.36</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>16.632</t>
+          <t>16.63</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4795,17 +4909,17 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>16.933</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>16.254</t>
+          <t>16.25</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -4815,6 +4929,7 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" s="7" t="n"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -4822,42 +4937,42 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>8.119</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10.003</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>7.883</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>8.579</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4867,17 +4982,17 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>9.477</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7.500</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -4887,6 +5002,7 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" s="6" t="n"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -4894,42 +5010,42 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>18.511</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>13.223</t>
+          <t>13.22</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>20.302</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
+          <t>20.30</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>18.715</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>17.668</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4939,17 +5055,17 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>19.748</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>17.947</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -4971,42 +5087,42 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>12.814</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>7.144</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>14.734</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+          <t>14.73</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>13.020</t>
+          <t>13.02</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>11.929</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5016,17 +5132,17 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14.757</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11.927</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5036,6 +5152,7 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" s="7" t="n"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>efetividade</t>
@@ -5043,42 +5160,42 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>16.030</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>8.630</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>18.537</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+          <t>18.54</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15.569</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>17.164</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5088,17 +5205,17 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>17.632</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>15.300</t>
+          <t>15.30</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5108,6 +5225,7 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" s="7" t="n"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>frequência</t>
@@ -5115,42 +5233,42 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>11.570</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>4.815</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13.858</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+          <t>13.86</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>11.075</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>13.376</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5160,17 +5278,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>13.041</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>10.898</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5180,6 +5298,7 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" s="6" t="n"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>essencialidade</t>
@@ -5187,42 +5306,42 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>18.192</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>12.956</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>19.966</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
+          <t>19.97</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18.041</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>18.333</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5232,17 +5351,17 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>19.243</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>17.713</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">

--- a/analise_formatada.xlsx
+++ b/analise_formatada.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,12 +40,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,9 +132,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -511,8 +502,8 @@
   <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -647,22 +638,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -672,42 +663,42 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -720,67 +711,67 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17.56</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -793,67 +784,67 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>(+)**</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8.82</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -866,67 +857,67 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17.88</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19.30</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -943,67 +934,67 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11.78</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -1016,62 +1007,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14.09</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1089,67 +1080,67 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6.79</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1162,67 +1153,67 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -1239,62 +1230,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12.73</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10.99</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1312,67 +1303,67 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16.81</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14.40</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1385,42 +1376,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11.85</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1430,17 +1421,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1458,62 +1449,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20.71</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1535,67 +1526,67 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13.33</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -1608,67 +1599,67 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15.85</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14.69</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12.31</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1681,42 +1672,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10.68</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1726,22 +1717,22 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1754,67 +1745,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19.30</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -1831,62 +1822,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12.90</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1904,62 +1895,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17.10</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1977,67 +1968,67 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>(+)***</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -2050,67 +2041,67 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17.41</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2118,67 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
+          <t>(+)**</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8.76</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2200,42 +2191,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2245,22 +2236,22 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2273,67 +2264,67 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2346,67 +2337,67 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15.49</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13.25</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="O26" s="9" t="inlineStr">
-        <is>
-          <t>(-)</t>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -2423,67 +2414,67 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12.59</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -2496,62 +2487,62 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17.74</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15.98</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15.80</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2569,67 +2560,67 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10.57</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2642,67 +2633,67 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2719,67 +2710,67 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14.94</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2792,67 +2783,67 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>16.68</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18.94</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -2865,17 +2856,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2885,47 +2876,47 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -2938,67 +2929,67 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18.60</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3015,62 +3006,62 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3088,67 +3079,67 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16.07</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3161,67 +3152,67 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -3234,67 +3225,67 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>18.42</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -3311,67 +3302,67 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -3384,62 +3375,62 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17.22</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3457,67 +3448,67 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
+          <t>(+)***</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>(-)***</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>8.04</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>10.36</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>9.10</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>8.28</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
         </is>
       </c>
     </row>
@@ -3530,42 +3521,42 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19.78</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3575,22 +3566,22 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3607,67 +3598,67 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11.68</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>(-)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)*</t>
         </is>
       </c>
     </row>
@@ -3680,37 +3671,37 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>17.02</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3720,22 +3711,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3753,67 +3744,67 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11.19</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3826,67 +3817,67 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19.79</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>17.83</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17.90</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -3903,67 +3894,67 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>10.02</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)**</t>
         </is>
       </c>
     </row>
@@ -3976,67 +3967,67 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>11.14</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
+          <t>(+)*</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>11.28</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>11.94</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>7.62</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>12.74</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4049,67 +4040,67 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4122,67 +4113,67 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17.59</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>(+)</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>16.30</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -4199,67 +4190,67 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)**</t>
         </is>
       </c>
     </row>
@@ -4272,62 +4263,62 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>18.39</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4345,42 +4336,42 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>13.88</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4390,22 +4381,22 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4418,42 +4409,42 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>20.82</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4463,17 +4454,17 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4495,67 +4486,67 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>11.19</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>(+)</t>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)*</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>9.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4568,67 +4559,67 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>15.22</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>12.65</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4641,67 +4632,67 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>9.17</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>(-)*</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>7.34</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>7.68</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4714,67 +4705,67 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>19.54</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>17.40</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>16.66</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4791,67 +4782,67 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>13.89</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4864,67 +4855,67 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>19.38</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16.36</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>16.25</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -4937,67 +4928,67 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>(+)*</t>
+          <t>(+)**</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -5010,67 +5001,67 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>20.30</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(+)</t>
         </is>
       </c>
     </row>
@@ -5087,62 +5078,62 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>14.73</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G63" s="8" t="inlineStr">
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>13.02</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>(-)*</t>
-        </is>
-      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5160,67 +5151,67 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>18.54</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>(+)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>(-)</t>
+          <t>(-)*</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>15.30</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -5233,42 +5224,42 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13.86</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>(+)*</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5278,22 +5269,22 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>
@@ -5306,67 +5297,67 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>19.97</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>(+)*</t>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>(-)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>18.33</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>(-)*</t>
+          <t>(-)</t>
         </is>
       </c>
     </row>

--- a/analise_formatada.xlsx
+++ b/analise_formatada.xlsx
@@ -3711,7 +3711,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>(+)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
